--- a/Result/profitability/1435.xlsx
+++ b/Result/profitability/1435.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08624999999999998</v>
+        <v>-0.1325</v>
       </c>
       <c r="N2" t="n">
-        <v>62.30499999999999</v>
+        <v>60.16999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06874999999999998</v>
+        <v>-0.1125</v>
       </c>
       <c r="N3" t="n">
-        <v>53.9175</v>
+        <v>53.02</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05499999999999998</v>
+        <v>-0.09749999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>48.22125</v>
+        <v>48.17375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05374999999999998</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>51.18375</v>
+        <v>51.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04624999999999998</v>
+        <v>-0.09374999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>53.51750000000001</v>
+        <v>53.45375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04999999999999998</v>
+        <v>-0.08624999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>55.97</v>
+        <v>55.9025</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03624999999999998</v>
+        <v>-0.08249999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>58.3175</v>
+        <v>58.32875</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.04624999999999997</v>
       </c>
       <c r="N9" t="n">
-        <v>59.36125</v>
+        <v>59.36125000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>-0.08</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3325</v>
+        <v>0.3325000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>72.52875</v>
@@ -9748,10 +9748,10 @@
         <v>-2</v>
       </c>
       <c r="J74" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="K74" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="L74" t="n">
         <v>-0.08</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-63</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-4223.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-63</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-63</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.14125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>67.45375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.09000000000000341</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001404494382022614</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6700000000000017</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01033312769895134</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
